--- a/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_files.xlsx
+++ b/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_files.xlsx
@@ -40,118 +40,118 @@
     <t>Er-In</t>
   </si>
   <si>
+    <t>1234749</t>
+  </si>
+  <si>
+    <t>450249_bi</t>
+  </si>
+  <si>
+    <t>1410412_bi</t>
+  </si>
+  <si>
+    <t>1300872_bi</t>
+  </si>
+  <si>
+    <t>457677_bi</t>
+  </si>
+  <si>
     <t>1920543</t>
   </si>
   <si>
+    <t>1634753</t>
+  </si>
+  <si>
+    <t>1710931</t>
+  </si>
+  <si>
+    <t>1840445</t>
+  </si>
+  <si>
+    <t>1229705</t>
+  </si>
+  <si>
+    <t>1925389</t>
+  </si>
+  <si>
+    <t>451606_bi</t>
+  </si>
+  <si>
+    <t>1818414</t>
+  </si>
+  <si>
+    <t>1814810</t>
+  </si>
+  <si>
+    <t>1140826</t>
+  </si>
+  <si>
+    <t>1234747</t>
+  </si>
+  <si>
+    <t>1538436_bi</t>
+  </si>
+  <si>
+    <t>1956508</t>
+  </si>
+  <si>
+    <t>1000761</t>
+  </si>
+  <si>
+    <t>451623_bi</t>
+  </si>
+  <si>
+    <t>1803318</t>
+  </si>
+  <si>
     <t>1233938</t>
   </si>
   <si>
     <t>1803512</t>
   </si>
   <si>
-    <t>1840445</t>
-  </si>
-  <si>
-    <t>1229705</t>
-  </si>
-  <si>
-    <t>1538436_bi</t>
-  </si>
-  <si>
-    <t>1925389</t>
-  </si>
-  <si>
-    <t>451606_bi</t>
-  </si>
-  <si>
-    <t>451623_bi</t>
-  </si>
-  <si>
-    <t>1818414</t>
-  </si>
-  <si>
-    <t>1140826</t>
-  </si>
-  <si>
-    <t>1234747</t>
-  </si>
-  <si>
-    <t>450249_bi</t>
-  </si>
-  <si>
-    <t>1410412_bi</t>
-  </si>
-  <si>
-    <t>1300872_bi</t>
-  </si>
-  <si>
-    <t>457677_bi</t>
-  </si>
-  <si>
-    <t>1634753</t>
-  </si>
-  <si>
-    <t>1710931</t>
-  </si>
-  <si>
-    <t>1956508</t>
-  </si>
-  <si>
-    <t>1000761</t>
-  </si>
-  <si>
-    <t>1234749</t>
-  </si>
-  <si>
-    <t>1814810</t>
-  </si>
-  <si>
-    <t>1803318</t>
+    <t>PuNi3</t>
+  </si>
+  <si>
+    <t>IrIn3</t>
   </si>
   <si>
     <t>Ho2CoGa8</t>
   </si>
   <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>Nd11Pd4In9</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>Ho6Co2Ga</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>Pr8CoGa3</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
+  </si>
+  <si>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
+    <t>Lu14Co2In3</t>
+  </si>
+  <si>
     <t>Ho10Ni9In20</t>
-  </si>
-  <si>
-    <t>Nd11Pd4In9</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>Ho6Co2Ga</t>
-  </si>
-  <si>
-    <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
-  </si>
-  <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>PuNi3</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>All files</t>
@@ -558,19 +558,19 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -584,13 +584,13 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -610,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -630,13 +630,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -645,10 +645,10 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -656,13 +656,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -671,10 +671,10 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -682,7 +682,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -694,13 +694,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -708,16 +708,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -734,7 +734,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -746,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -760,13 +760,13 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -786,22 +786,22 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -812,25 +812,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -838,25 +838,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -864,25 +864,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -890,25 +890,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -922,19 +922,19 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -948,19 +948,19 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -980,13 +980,13 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -994,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1009,10 +1009,10 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1046,22 +1046,22 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1072,25 +1072,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1098,25 +1098,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1130,19 +1130,19 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">

--- a/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_files.xlsx
+++ b/20240519_ErCoIn_ternary_binary_combine/output/system_analysis/system_analysis_files.xlsx
@@ -40,9 +40,42 @@
     <t>Er-In</t>
   </si>
   <si>
+    <t>1803318</t>
+  </si>
+  <si>
     <t>1234749</t>
   </si>
   <si>
+    <t>1920543</t>
+  </si>
+  <si>
+    <t>1233938</t>
+  </si>
+  <si>
+    <t>1803512</t>
+  </si>
+  <si>
+    <t>451623_bi</t>
+  </si>
+  <si>
+    <t>1814810</t>
+  </si>
+  <si>
+    <t>451606_bi</t>
+  </si>
+  <si>
+    <t>1634753</t>
+  </si>
+  <si>
+    <t>1710931</t>
+  </si>
+  <si>
+    <t>1925389</t>
+  </si>
+  <si>
+    <t>1818414</t>
+  </si>
+  <si>
     <t>450249_bi</t>
   </si>
   <si>
@@ -55,13 +88,13 @@
     <t>457677_bi</t>
   </si>
   <si>
-    <t>1920543</t>
-  </si>
-  <si>
-    <t>1634753</t>
-  </si>
-  <si>
-    <t>1710931</t>
+    <t>1956508</t>
+  </si>
+  <si>
+    <t>1000761</t>
+  </si>
+  <si>
+    <t>1538436_bi</t>
   </si>
   <si>
     <t>1840445</t>
@@ -70,88 +103,55 @@
     <t>1229705</t>
   </si>
   <si>
-    <t>1925389</t>
-  </si>
-  <si>
-    <t>451606_bi</t>
-  </si>
-  <si>
-    <t>1818414</t>
-  </si>
-  <si>
-    <t>1814810</t>
-  </si>
-  <si>
     <t>1140826</t>
   </si>
   <si>
     <t>1234747</t>
   </si>
   <si>
-    <t>1538436_bi</t>
-  </si>
-  <si>
-    <t>1956508</t>
-  </si>
-  <si>
-    <t>1000761</t>
-  </si>
-  <si>
-    <t>451623_bi</t>
-  </si>
-  <si>
-    <t>1803318</t>
-  </si>
-  <si>
-    <t>1233938</t>
-  </si>
-  <si>
-    <t>1803512</t>
+    <t>Lu14Co2In3</t>
   </si>
   <si>
     <t>PuNi3</t>
   </si>
   <si>
+    <t>Ho2CoGa8</t>
+  </si>
+  <si>
+    <t>Ho10Ni9In20</t>
+  </si>
+  <si>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
+  </si>
+  <si>
+    <t>Ho6Co2Ga</t>
+  </si>
+  <si>
     <t>IrIn3</t>
   </si>
   <si>
-    <t>Ho2CoGa8</t>
-  </si>
-  <si>
-    <t>HoCoGa5</t>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
   </si>
   <si>
     <t>Nd11Pd4In9</t>
   </si>
   <si>
-    <t>MgCu4Sn</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>Ho6Co2Ga</t>
-  </si>
-  <si>
-    <t>Gd14Co3In2.7</t>
-  </si>
-  <si>
     <t>Pr8CoGa3</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>Lu3Co2In4</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>Lu14Co2In3</t>
-  </si>
-  <si>
-    <t>Ho10Ni9In20</t>
   </si>
   <si>
     <t>All files</t>
@@ -558,19 +558,19 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -584,19 +584,19 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -616,13 +616,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -630,19 +630,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -656,19 +656,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -694,13 +694,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -708,25 +708,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -734,7 +734,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -746,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -760,25 +760,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -786,25 +786,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -812,7 +812,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -838,25 +838,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -864,25 +864,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -890,25 +890,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -916,25 +916,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -942,25 +942,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -968,22 +968,22 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1020,22 +1020,22 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1046,13 +1046,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>2</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1084,13 +1084,13 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1104,19 +1104,19 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1130,19 +1130,19 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:8">
